--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 05/XKSX_LinhKienGiaCongVNSH03_090526.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 05/XKSX_LinhKienGiaCongVNSH03_090526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CC5833-26F2-4BD8-8C74-734B1D1D962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91B4EC1-E393-4CA1-BC38-79314BB94BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1055,9 +1055,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>475559</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>475560</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>164224</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1441,11 +1441,11 @@
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" style="1" customWidth="1"/>
     <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" style="1" customWidth="1"/>
-    <col min="8" max="10" width="16.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="10" width="16.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="21.85546875" style="1" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="20.42578125" style="1" customWidth="1"/>
     <col min="13" max="13" width="24.85546875" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="D74" s="16">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="E74" s="15"/>
       <c r="F74" s="15"/>
@@ -3569,7 +3569,9 @@
       <c r="L74" s="16">
         <v>495</v>
       </c>
-      <c r="M74" s="16"/>
+      <c r="M74" s="16">
+        <v>495</v>
+      </c>
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="15">
@@ -5840,7 +5842,7 @@
     <mergeCell ref="G96:G128"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <rowBreaks count="4" manualBreakCount="4">
     <brk id="30" max="7" man="1"/>
     <brk id="63" max="7" man="1"/>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 05/XKSX_LinhKienGiaCongVNSH03_090526.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 05/XKSX_LinhKienGiaCongVNSH03_090526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91B4EC1-E393-4CA1-BC38-79314BB94BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD33DD07-6356-4E8A-8FD9-A4C8EFB76B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1055,7 +1055,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>475560</xdr:colOff>
+      <xdr:colOff>475559</xdr:colOff>
       <xdr:row>137</xdr:row>
       <xdr:rowOff>164224</xdr:rowOff>
     </xdr:to>
@@ -1445,7 +1445,7 @@
     <col min="6" max="6" width="15.7109375" style="1" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="19.140625" style="1" hidden="1" customWidth="1"/>
     <col min="8" max="10" width="16.5703125" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="21.85546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="20.42578125" style="1" customWidth="1"/>
     <col min="13" max="13" width="24.85546875" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
@@ -4137,7 +4137,7 @@
         <v>194</v>
       </c>
       <c r="L93" s="16">
-        <v>1785</v>
+        <v>21090</v>
       </c>
       <c r="M93" s="16">
         <v>21090</v>
